--- a/artfynd/A 36034-2024 artfynd.xlsx
+++ b/artfynd/A 36034-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120109273</v>
+        <v>120109274</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>91863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,46 +807,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580618</v>
+        <v>580703</v>
       </c>
       <c r="R3" t="n">
-        <v>6508191</v>
+        <v>6508242</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120109275</v>
+        <v>120109273</v>
       </c>
       <c r="B4" t="n">
-        <v>91863</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,22 +948,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580596</v>
+        <v>580618</v>
       </c>
       <c r="R4" t="n">
-        <v>6508219</v>
+        <v>6508191</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120109274</v>
+        <v>120109275</v>
       </c>
       <c r="B5" t="n">
         <v>91863</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580703</v>
+        <v>580596</v>
       </c>
       <c r="R5" t="n">
-        <v>6508242</v>
+        <v>6508219</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36034-2024 artfynd.xlsx
+++ b/artfynd/A 36034-2024 artfynd.xlsx
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120109273</v>
+        <v>120109275</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>91863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,27 +948,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580618</v>
+        <v>580596</v>
       </c>
       <c r="R4" t="n">
-        <v>6508191</v>
+        <v>6508219</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120109275</v>
+        <v>120109273</v>
       </c>
       <c r="B5" t="n">
-        <v>91863</v>
+        <v>57326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,21 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,22 +1067,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580596</v>
+        <v>580618</v>
       </c>
       <c r="R5" t="n">
-        <v>6508219</v>
+        <v>6508191</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36034-2024 artfynd.xlsx
+++ b/artfynd/A 36034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120109277</v>
+        <v>120109275</v>
       </c>
       <c r="B2" t="n">
-        <v>94681</v>
+        <v>91863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580778</v>
+        <v>580596</v>
       </c>
       <c r="R2" t="n">
-        <v>6508250</v>
+        <v>6508219</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120109274</v>
+        <v>120109277</v>
       </c>
       <c r="B3" t="n">
-        <v>91863</v>
+        <v>94681</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +806,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580703</v>
+        <v>580778</v>
       </c>
       <c r="R3" t="n">
-        <v>6508242</v>
+        <v>6508250</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120109275</v>
+        <v>120109274</v>
       </c>
       <c r="B4" t="n">
         <v>91863</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580596</v>
+        <v>580703</v>
       </c>
       <c r="R4" t="n">
-        <v>6508219</v>
+        <v>6508242</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 36034-2024 artfynd.xlsx
+++ b/artfynd/A 36034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120109275</v>
+        <v>120109276</v>
       </c>
       <c r="B2" t="n">
-        <v>91863</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580596</v>
+        <v>580778</v>
       </c>
       <c r="R2" t="n">
-        <v>6508219</v>
+        <v>6508250</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120109277</v>
+        <v>120109273</v>
       </c>
       <c r="B3" t="n">
-        <v>94681</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,42 +803,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580778</v>
+        <v>580618</v>
       </c>
       <c r="R3" t="n">
-        <v>6508250</v>
+        <v>6508191</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120109274</v>
+        <v>120109275</v>
       </c>
       <c r="B4" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -957,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580703</v>
+        <v>580596</v>
       </c>
       <c r="R4" t="n">
-        <v>6508242</v>
+        <v>6508219</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120109273</v>
+        <v>120109274</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,46 +1050,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580618</v>
+        <v>580703</v>
       </c>
       <c r="R5" t="n">
-        <v>6508191</v>
+        <v>6508242</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36034-2024 artfynd.xlsx
+++ b/artfynd/A 36034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120109276</v>
+        <v>120109274</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580778</v>
+        <v>580703</v>
       </c>
       <c r="R2" t="n">
-        <v>6508250</v>
+        <v>6508242</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120109273</v>
+        <v>120109277</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,50 +806,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580618</v>
+        <v>580778</v>
       </c>
       <c r="R3" t="n">
-        <v>6508191</v>
+        <v>6508250</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1034,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120109274</v>
+        <v>120109273</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,41 +1045,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580703</v>
+        <v>580618</v>
       </c>
       <c r="R5" t="n">
-        <v>6508242</v>
+        <v>6508191</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36034-2024 artfynd.xlsx
+++ b/artfynd/A 36034-2024 artfynd.xlsx
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120109275</v>
+        <v>120109273</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,22 +948,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580596</v>
+        <v>580618</v>
       </c>
       <c r="R4" t="n">
-        <v>6508219</v>
+        <v>6508191</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120109273</v>
+        <v>120109275</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,21 +1050,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,27 +1072,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580618</v>
+        <v>580596</v>
       </c>
       <c r="R5" t="n">
-        <v>6508191</v>
+        <v>6508219</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36034-2024 artfynd.xlsx
+++ b/artfynd/A 36034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120109274</v>
+        <v>120109273</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,41 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580703</v>
+        <v>580618</v>
       </c>
       <c r="R2" t="n">
-        <v>6508242</v>
+        <v>6508191</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120109277</v>
+        <v>120109274</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +811,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580778</v>
+        <v>580703</v>
       </c>
       <c r="R3" t="n">
-        <v>6508250</v>
+        <v>6508242</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120109273</v>
+        <v>120109276</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,50 +930,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580618</v>
+        <v>580778</v>
       </c>
       <c r="R4" t="n">
-        <v>6508191</v>
+        <v>6508250</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 36034-2024 artfynd.xlsx
+++ b/artfynd/A 36034-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120109273</v>
+        <v>120109277</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580618</v>
+        <v>580778</v>
       </c>
       <c r="R2" t="n">
-        <v>6508191</v>
+        <v>6508250</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -918,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120109276</v>
+        <v>120109273</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,42 +922,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580778</v>
+        <v>580618</v>
       </c>
       <c r="R4" t="n">
-        <v>6508250</v>
+        <v>6508191</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 36034-2024 artfynd.xlsx
+++ b/artfynd/A 36034-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120109277</v>
+        <v>120109276</v>
       </c>
       <c r="B2" t="n">
         <v>94704</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120109274</v>
+        <v>120109275</v>
       </c>
       <c r="B3" t="n">
         <v>91881</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580703</v>
+        <v>580596</v>
       </c>
       <c r="R3" t="n">
-        <v>6508242</v>
+        <v>6508219</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1034,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120109275</v>
+        <v>120109274</v>
       </c>
       <c r="B5" t="n">
         <v>91881</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580596</v>
+        <v>580703</v>
       </c>
       <c r="R5" t="n">
-        <v>6508219</v>
+        <v>6508242</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36034-2024 artfynd.xlsx
+++ b/artfynd/A 36034-2024 artfynd.xlsx
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120109273</v>
+        <v>120109274</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,46 +926,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580618</v>
+        <v>580703</v>
       </c>
       <c r="R4" t="n">
-        <v>6508191</v>
+        <v>6508242</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -997,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120109274</v>
+        <v>120109273</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,41 +1045,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580703</v>
+        <v>580618</v>
       </c>
       <c r="R5" t="n">
-        <v>6508242</v>
+        <v>6508191</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
